--- a/Reference Data/XLSX Workbooks/Internal CC Lists.xlsx
+++ b/Reference Data/XLSX Workbooks/Internal CC Lists.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arch Aerial WS 01\Documents\Data Team\Steven\Dailies Email Templates\Reference Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arch Aerial WS 01\Documents\Data Team\Steven\Customer Email Builder\Reference Data\XLSX Workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D45FE5-C7A2-4CCA-8CC9-C1C0222DFB70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5B59A6-F2C3-4462-9CEE-AD6AF9F2ACC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-16440" windowWidth="38640" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Steven" sheetId="1" r:id="rId1"/>
-    <sheet name="Doug" sheetId="2" r:id="rId2"/>
+    <sheet name="Doug" sheetId="1" r:id="rId1"/>
+    <sheet name="Steven" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="10">
   <si>
     <t>Commercial Construction</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>dsimpson@archaerial.com</t>
-  </si>
-  <si>
-    <t>msweisthal@archaerial.com</t>
   </si>
   <si>
     <t>smclaren@archaerial.com</t>
@@ -425,12 +422,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28.28515625" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -482,14 +475,9 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -499,12 +487,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{326773E8-2C0F-4737-B0F1-2FBA241AAD70}">
-  <dimension ref="A1:B8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="1" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -557,22 +544,13 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A7" r:id="rId1" xr:uid="{9C0D5212-21C3-440E-9FFF-9B17F4AB58EC}"/>
-    <hyperlink ref="B7" r:id="rId2" xr:uid="{489597AE-1961-4D9E-9D53-DC6A60540491}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Reference Data/XLSX Workbooks/Internal CC Lists.xlsx
+++ b/Reference Data/XLSX Workbooks/Internal CC Lists.xlsx
@@ -1,74 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arch Aerial WS 01\Documents\Data Team\Steven\Customer Email Builder\Reference Data\XLSX Workbooks\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5B59A6-F2C3-4462-9CEE-AD6AF9F2ACC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Doug" sheetId="1" r:id="rId1"/>
-    <sheet name="Steven" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doug" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steven" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="10">
-  <si>
-    <t>Commercial Construction</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas</t>
-  </si>
-  <si>
-    <t>rbaker@archaerial.com</t>
-  </si>
-  <si>
-    <t>rbusby@archaerial.com</t>
-  </si>
-  <si>
-    <t>davant@archaerial.com</t>
-  </si>
-  <si>
-    <t>sshockley@archaerial.com</t>
-  </si>
-  <si>
-    <t>tbrown@archaerial.com</t>
-  </si>
-  <si>
-    <t>jalameda@archaerial.com</t>
-  </si>
-  <si>
-    <t>dsimpson@archaerial.com</t>
-  </si>
-  <si>
-    <t>smclaren@archaerial.com</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -87,21 +48,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -421,64 +441,96 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Commercial Construction</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rbaker@archaerial.com</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>rbaker@archaerial.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rbusby@archaerial.com</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>davant@archaerial.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sshockley@archaerial.com</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sshockley@archaerial.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tbrown@archaerial.com</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tbrown@archaerial.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>jalameda@archaerial.com</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>jalameda@archaerial.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>smclaren@archaerial.com</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>smclaren@archaerial.com</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -487,67 +539,125 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col width="25.7109375" bestFit="1" customWidth="1" min="1" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Commercial Construction</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>rbaker@archaerial.com</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>rbaker@archaerial.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>rbusby@archaerial.com</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>davant@archaerial.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sshockley@archaerial.com</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sshockley@archaerial.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tbrown@archaerial.com</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tbrown@archaerial.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>jalameda@archaerial.com</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>jalameda@archaerial.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dsimpson@archaerial.com</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dsimpson@archaerial.com</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Commercial Construction</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Reference Data/XLSX Workbooks/Internal CC Lists.xlsx
+++ b/Reference Data/XLSX Workbooks/Internal CC Lists.xlsx
@@ -9,6 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doug" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steven" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__pycache__" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -663,4 +664,30 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Commercial Construction</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Oil &amp; Gas</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>